--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9A座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7667,2081 +7529,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第2B期 - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>50 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>40 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2116呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 2116呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-$4,870万
-$42,019/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-$4,687万
-$40,510/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-$4,830万
-$41,674/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-$5,089万
-$43,912/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1157呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1159呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1156呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="16" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 829呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 826呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 507呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第2B期 - 9A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1088呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1084呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1086呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 832呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第2B期 - 9座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>H.MANOR</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>H.SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>H.SKYPLEX | 3537呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>H.MANOR | 2673呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 2125呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 2171呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 2184呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 2201呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 2197呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 2190呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 2179呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 2167呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 2144呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 2133呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1861呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1400呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9A座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -7529,4 +7710,2081 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2116呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 2116呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+$4870万
+$42,019/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+$4687万
+$40,510/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+$4830万
+$41,674/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+$5089万
+$43,912/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1157呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1159呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1156呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 829呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 826呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 507呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>9A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1088呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1084呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1086呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 832呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>9座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>H.MANOR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>H.SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>H.SKYPLEX | 3537呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>H.MANOR | 2673呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 2125呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 2171呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 2184呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 2201呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 2197呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 2190呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 2179呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 2167呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 2144呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 2133呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1861呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1400呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -715,6 +719,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -765,6 +789,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -815,6 +859,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -865,6 +929,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -915,6 +999,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -965,6 +1069,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1015,6 +1139,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1065,6 +1209,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1115,6 +1279,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1165,6 +1349,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1215,6 +1419,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1265,6 +1489,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1315,6 +1559,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1365,6 +1629,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1415,6 +1699,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1465,6 +1769,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1515,6 +1839,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1565,6 +1909,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1615,6 +1979,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1661,6 +2045,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1707,6 +2111,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1757,6 +2181,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1803,6 +2247,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1853,6 +2317,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1903,6 +2387,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1953,6 +2457,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2003,6 +2527,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2053,6 +2597,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2099,6 +2663,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2149,6 +2733,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2199,6 +2803,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2249,6 +2873,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2299,6 +2943,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2349,6 +3013,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2399,6 +3083,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2449,6 +3153,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2499,6 +3223,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2549,6 +3293,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2599,6 +3363,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2649,6 +3433,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2699,6 +3503,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2749,6 +3573,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2799,6 +3643,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2849,6 +3713,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2899,6 +3783,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2949,6 +3853,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2999,6 +3923,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3049,6 +3993,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3099,6 +4063,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3149,6 +4133,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3199,6 +4203,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3249,6 +4273,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3299,6 +4343,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3349,6 +4413,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3399,6 +4483,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3449,6 +4553,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3499,6 +4623,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3549,6 +4693,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3599,6 +4763,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3649,6 +4833,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3699,6 +4903,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3749,6 +4973,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3799,6 +5043,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3849,6 +5113,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3899,6 +5183,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3949,6 +5253,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3999,6 +5323,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4049,6 +5393,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4099,6 +5463,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4149,6 +5533,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4199,6 +5603,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4249,6 +5673,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4299,6 +5743,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4349,6 +5813,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4399,6 +5883,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4449,6 +5953,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4499,6 +6023,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4549,6 +6093,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4599,6 +6163,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4649,6 +6233,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4699,6 +6303,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4749,6 +6373,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4799,6 +6443,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4849,6 +6513,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4899,6 +6583,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4949,6 +6653,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4999,6 +6723,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5049,6 +6793,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5099,6 +6863,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5149,6 +6933,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5199,6 +7003,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5249,6 +7073,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5299,6 +7143,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5349,6 +7213,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5399,6 +7283,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5449,6 +7353,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5499,6 +7423,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5549,6 +7493,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5599,6 +7563,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5649,6 +7633,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5699,6 +7703,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5749,6 +7773,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5799,6 +7843,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5849,6 +7913,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5899,6 +7983,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5949,6 +8053,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5999,6 +8123,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6049,6 +8193,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6099,6 +8263,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6149,6 +8333,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6199,6 +8403,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6249,6 +8473,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6299,6 +8543,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6349,6 +8613,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6399,6 +8683,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6449,6 +8753,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6499,6 +8823,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6549,6 +8893,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6599,6 +8963,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6649,6 +9033,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6699,6 +9103,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6749,6 +9173,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6799,6 +9243,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6849,6 +9313,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6899,6 +9383,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6949,6 +9453,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6999,6 +9523,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7049,6 +9593,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7099,6 +9663,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7149,6 +9733,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7199,6 +9803,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7249,6 +9873,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7299,6 +9943,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7349,6 +10013,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7399,6 +10083,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7449,6 +10153,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7499,6 +10223,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7549,6 +10293,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7599,6 +10363,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7649,6 +10433,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7699,13 +10503,33 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8089,7 +10913,7 @@
           <t>A | 1159呎 (4+房)
 $4870万
 $42,019/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -8097,7 +10921,7 @@
           <t>B | 1157呎 (4+房)
 $4687万
 $40,510/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -8115,7 +10939,7 @@
           <t>A | 1159呎 (4+房)
 $4830万
 $41,674/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -8193,7 +11017,7 @@
           <t>A | 1159呎 (4+房)
 $5089万
 $43,912/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -10913,7 +10913,7 @@
           <t>A | 1159呎 (4+房)
 $4870万
 $42,019/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -10921,7 +10921,7 @@
           <t>B | 1157呎 (4+房)
 $4687万
 $40,510/呎
-(26年-06月-25日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
           <t>A | 1159呎 (4+房)
 $4830万
 $41,674/呎
-(26年-07月-04日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>A | 1159呎 (4+房)
 $5089万
 $43,912/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -10913,7 +10913,7 @@
           <t>A | 1159呎 (4+房)
 $4870万
 $42,019/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -10921,7 +10921,7 @@
           <t>B | 1157呎 (4+房)
 $4687万
 $40,510/呎
-(26年-07月)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
           <t>A | 1159呎 (4+房)
 $4830万
 $41,674/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>A | 1159呎 (4+房)
 $5089万
 $43,912/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/files/九龙-启德-天玺．海第2B期.xlsx
@@ -2236,7 +2236,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -10939,7 +10939,7 @@
           <t>A | 1159呎 (4+房)
 $4830万
 $41,674/呎
-(26年-07月-04日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
